--- a/brands/braveyong/braveyong_misc_815-chat-blast-10cases.xlsx
+++ b/brands/braveyong/braveyong_misc_815-chat-blast-10cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="815 단톡방 멘트 10종" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="815 도발 후킹 멘트 10종" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 가이드" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -451,9 +451,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,232 +469,205 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>멘트 (복붙용)</t>
+          <t>멘트 (복붙용 — 첫 줄이 도발 후킹)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>추천 채널</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="110" customHeight="1">
+          <t>글자수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>매출 정지 공포</t>
+          <t>매출 정지</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>8월부터 유니패스에 업체 등록 안 된 사업자는 수입신고 자체가 안 됩니다.
-통관이 멈추면 매출도 멈추는데, 아직 준비한 분이 거의 없더라고요.
-대기업 공인인증서 담당 출신이 인증서 쉽게 발급받는 법부터 유니패스 등록까지 원스탑으로 알려준답니다.
-6/21(일) 라이브 단 1회, 6/20 결제 마감.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="110" customHeight="1">
+          <t>8월에 멈출 스토어, 지금 정해지고 있습니다.
+유니패스 등록 없으면 수입신고가 안 되고, 수입신고가 없으면 매출도 없습니다.
+대기업 공인인증서 담당 출신이 인증서 발급부터 유니패스 등록까지 원스탑으로 끝내드립니다.
+6/21(일) 단 1회 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>통장 산수 (한 달에 하나)</t>
+          <t>통장 산수</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>사업자는 5개, 10개인데 통장은 한 달에 하나밖에 못 만듭니다.
-이 산수, 어떻게 푸시겠어요? 지금 시작해도 8월 전에 빠듯해요.
-통장 한 개도 더 안 만들고 사업자 인증서 받는, 아무도 모르는 방법이 있답니다.
-대기업 공인인증서 담당 출신이 6/21(일) 라이브에서 유니패스 등록까지 순서대로 보여줍니다.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="110" customHeight="1">
+          <t>사업자 10개, 통장은 한 달에 1개. 이 산수 못 풀면 구매대행 끝입니다.
+통장 한 개도 더 안 만들고 인증서까지 끝내는 방법, 아는 사람만 압니다.
+대기업에서 공인인증서 만들던 사람이 직접 보여줍니다.
+6/21(일) 라이브 단 1회 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>은행 20영업일 줄서기</t>
+          <t>'기다려보자'의 값</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>급해서 은행 창구 가면 "20영업일 뒤에 오세요" 소리 듣습니다.
-7월에 시작하면 한 번만 꼬여도 8월 데드라인 넘어가요.
-이 줄에 안 서고 인증서 받는 방법, 대기업에서 공인인증서 만들던 분이 직접 풉니다.
-필요한 서류부터 스텝별 할 일·주의할 점까지 원스탑 정리. 6/21(일) 단 1회.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="110" customHeight="1">
+          <t>'기다려보자'는 분들 — 지금 제일 비싼 선택 중입니다.
+기다리는 동안 통장 개설 한도, 20영업일, 8월 데드라인이 다 지나갑니다.
+서류부터 유니패스 등록까지 90분 원스탑 — 대기업 공인인증서 담당 출신 진행.
+6/20 결제 마감 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>사업자별 각각 등록·인증서</t>
+          <t>20영업일 줄서기</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>유니패스 공지 보셨어요? 사업자별로 각각 등록, 인증서도 각각입니다.
-사업자 10개면 인증서 10개… 어떻게 하실 계획이세요?
-사업자별 필요 서류 체크부터 대량 처리 동선까지, 하루에 끝내는 순서를 알려주는 라이브가 있어 공유합니다.
-대기업 공인인증서 담당 출신 + 현직 셀러 직접 진행, 6/21(일) 단 1회.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="110" customHeight="1">
+          <t>은행 가서 "20영업일 뒤에 오세요" 듣고 오실 겁니까?
+그 줄에 안 서는 방법이 따로 있습니다.
+대기업 공인인증서 담당 출신이 필요 서류·스텝별 할 일·주의할 점까지 다 풉니다.
+6/21(일) 밤 8시 단 1회 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>유료 인증서 매년 비용</t>
+          <t>재등록 함정</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>유료 인증서로 가면 사업자 20개 기준 연 40만 원, 매년 나갑니다.
-0원으로 끝내는 경로가 있는데 아는 사람이 거의 없어요.
-대기업에서 공인인증서 만들던 사람이 그 방법부터 유니패스 등록까지 원스탑으로 공개합니다.
-한 번 배우면 매년 갱신까지 계속 내 것. 6/21(일) 라이브, 6/20 마감.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
+          <t>"예전에 등록 다 해놨는데?" — 그게 제일 위험한 착각입니다.
+기존 등록자도 신규 시스템에서 재등록 대상, 사업자별로 각각입니다.
+내 사업자 1분 판별부터 유니패스 등록까지 원스탑.
+6/21(일) 라이브 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>환불 = 내 돈 (구매대행 구조)</t>
+          <t>유료 인증서 비용</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>구매대행은 현지 결제가 먼저라, 통관이 멈추면 환불은 곧 내 돈입니다.
-8월부터 등록 없인 수입신고가 안 되는데, 환불 폭탄부터 맞으실 건가요?
-인증서 쉽게 받는 법 → 유니패스 등록까지, 막히기 전에 원스탑으로 끝내는 라이브가 있습니다.
-6/21(일) 밤 8시 단 1회, 대기업 공인인증서 담당 출신 진행.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="110" customHeight="1">
+          <t>인증서에 매년 40만 원씩 내실 겁니까? 0원 경로가 있는데.
+사업자 20개 기준 유료 인증서 연 40만 원 — 매년 반복입니다.
+대기업에서 공인인증서 만들던 사람이 0원으로 끝내는 경로를 공개합니다.
+한 번 배우면 매년 내 것 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>재등록 함정 (기존 등록자)</t>
+          <t>환불 폭탄</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>"예전에 구매대행 등록 다 해놨는데?" — 이게 제일 위험한 착각입니다.
-기존 등록자도 신규 시스템에서 재등록 대상이에요. 사업자별로 각각.
-내 사업자가 대상인지 1분 판별부터 서류 준비, 유니패스 등록까지 스텝별로 정리해주는 자리가 있어 공유합니다.
-대기업 공인인증서 담당 출신, 6/21(일) 라이브 단 1회.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>단톡방·채널 공용</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="110" customHeight="1">
+          <t>준비 없으면 환불 폭탄은 8월에 터집니다.
+구매대행은 현지 결제가 먼저 — 통관 멈추면 환불은 곧 내 돈입니다.
+막히기 전에 인증서부터 유니패스 등록까지 원스탑으로 끝내세요.
+6/21(일) 단 1회, 6/20 마감 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>'기다려보자'의 위험</t>
+          <t>정책 윈도우</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>단톡방마다 "일단 기다려보자"는 말 돌죠. 기다리는 동안 마감은 옵니다.
-그 방에 답 아는 사람, 한 명도 없지 않나요?
-인증서 발급부터 유니패스 등록까지 원스탑으로 정리해주는 사람이 있습니다 — 대기업 공인인증서 담당 출신.
-6/21(일) 밤 8시, 90분 + Q&amp;A 단 1회. 질문 들고 오세요.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>단톡방 공유용</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="110" customHeight="1">
+          <t>지금은 됩니다. 언제까지 될지는 아무도 모릅니다.
+은행 정책에 기대는 길 — 사람이 몰리면 조여질 수 있습니다.
+되는 지금 배우고 다음 날 바로 발급받으세요. 대기업 공인인증서 담당 출신이 안내합니다.
+6/20 결제 마감 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>정책 윈도우 (지금 되는 방법)</t>
+          <t>단톡방엔 답이 없다</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>지금은 되는 방법이 있습니다. 문제는 언제까지 될지 아무도 모른다는 것.
-은행 정책에 기대는 길이라 사람이 몰리면 조여질 수 있어요.
-되는 지금 배우고, 다음 날 서류 들고 바로 발급받는 게 가장 확실합니다.
-스텝별 할 일·주의할 점까지 원스탑 — 6/21(일) 단 1회, 6/20 결제 마감.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>카카오채널 공지용</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="110" customHeight="1">
+          <t>단톡방에서 답 찾고 계시죠? 그 방에 답 아는 사람 없습니다.
+도는 건 "기다려보자"뿐 — 기다리는 동안 마감이 옵니다.
+대기업 공인인증서 담당 출신에게 90분 + Q&amp;A로 다 물어보세요.
+6/21(일) 밤 8시 단 1회 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -705,17 +678,14 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>8월 어느 아침, 배대지 알림 — "통관 보류, 통관고유부호 미기재."
-스토어엔 "배송 언제 되나요" 문의가 쌓이는데 답할 말이 없습니다.
-이 아침을 안 만나는 준비, 90분이면 끝납니다. 서류 체크부터 유니패스 등록까지 원스탑.
-대기업 공인인증서 담당 출신이 6/21(일) 밤 8시에 처음부터 끝까지 보여드립니다.
-https://gigclass.kr/815</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>카카오채널 공지용</t>
-        </is>
+          <t>8월 어느 아침, 첫 알림이 "통관 보류"면 그날 매출은 0원입니다.
+답장 못 할 "배송 언제 되나요"가 쌓이기 시작합니다.
+그 아침을 안 만나는 준비, 서류부터 등록까지 90분이면 끝납니다.
+6/21(일) 라이브 ▶ https://gigclass.kr/815</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -738,7 +708,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>■ 815 단톡방·카카오채널 홍보 멘트 10종 — 공포 + 전문가 해결 공식</t>
+          <t>■ 815 단톡방·카카오채널 도발 후킹 멘트 10종 (v2 — 짧고 굵게)</t>
         </is>
       </c>
     </row>
@@ -748,70 +718,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 멘트는 C열 그대로 복사해 붙이면 됩니다 (4~5줄, 링크 포함).</t>
+          <t>구조: 1줄 도발 후킹 → 1줄 공포 구체화 → 1줄 전문가 해결(원스탑) → 1줄 CTA+링크</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2. 같은 방에 여러 번 뿌릴 땐 다른 번호를 돌려쓰세요 (도배 인식 방지).</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. 카피 원칙 (수정 시에도 유지):</t>
+          <t>1. C열 그대로 복사해 붙이세요. 한 방에는 번호를 돌려가며(도배 인식 방지).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - '8.15'·'8월 15일' 등 구체 일자 금지 → '8월부터'만 사용</t>
+          <t>2. 수정할 때 깨면 안 되는 룰:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - '선착순·정원' 수치 금지 → 긴급성은 6/20 마감·단 1회로만</t>
+          <t xml:space="preserve">   - 구체 일자 금지 → '8월'만 ('8.15', '8월 15일' 금지)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - '곧 막힌다' 단정 금지 → '언제 막힐지 모른다 / 지금 되는 게 확실' 톤</t>
+          <t xml:space="preserve">   - 선착순·정원 수치 금지 → 긴급성은 6/20 마감·단 1회로만</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 크레덴셜은 '대기업 공인인증서 담당 출신' (전직 은행원 표현 금지)</t>
+          <t xml:space="preserve">   - '곧 막힌다' 단정 금지 → '언제까지 될지 모른다' 톤 유지</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4. 핵심 가치 제안: 인증서 쉽게 발급받는 아무도 모르는 방법 + 유니패스 등록까지</t>
+          <t xml:space="preserve">   - 크레덴셜은 '대기업 공인인증서 담당 출신' 고정</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   원스탑 + 필요 서류·스텝별 할 일·주의할 점.</t>
+          <t>3. 가치 제안: 인증서 쉽게 발급받는 아무도 모르는 방법 + 유니패스 등록까지 원스탑</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5. 링크: https://gigclass.kr/815 (결제 완료 시 오픈채팅 입장 문자 자동 발송)</t>
+          <t xml:space="preserve">   + 필요 서류·스텝별 할 일·주의할 점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4. 링크: https://gigclass.kr/815 (결제 시 오픈채팅 입장 문자 자동 발송)</t>
         </is>
       </c>
     </row>
